--- a/KatalonData/Bootstrap/VT-Data-Prod.xlsx
+++ b/KatalonData/Bootstrap/VT-Data-Prod.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2408" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2560" uniqueCount="361">
   <si>
     <t>AppIDDemo</t>
   </si>
@@ -1002,6 +1002,120 @@
   </si>
   <si>
     <t>Wed Mar 11 08:19:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:16:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:18:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:20:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:21:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:23:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:25:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:27:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:28:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:29:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:31:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:32:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:33:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:08:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:09:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:10:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:11:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:12:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:12:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:13:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:14:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:15:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:16:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:17:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:18:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:19:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:20:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:21:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:22:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:23:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:24:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:24:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:26:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:26:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:28:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:28:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:29:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:31:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 22:32:08 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1463,7 +1577,7 @@
         <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>311</v>
+        <v>349</v>
       </c>
       <c r="C2" t="s">
         <v>78</v>
@@ -1564,7 +1678,7 @@
         <v>78</v>
       </c>
       <c r="B3" t="s">
-        <v>312</v>
+        <v>350</v>
       </c>
       <c r="C3" t="s">
         <v>78</v>
@@ -1665,7 +1779,7 @@
         <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>313</v>
+        <v>351</v>
       </c>
       <c r="C4" t="s">
         <v>78</v>
@@ -1766,7 +1880,7 @@
         <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>314</v>
+        <v>352</v>
       </c>
       <c r="C5" t="s">
         <v>78</v>
@@ -1995,7 +2109,7 @@
         <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>315</v>
+        <v>353</v>
       </c>
       <c r="C2" t="s">
         <v>78</v>
@@ -2099,7 +2213,7 @@
         <v>78</v>
       </c>
       <c r="B3" t="s">
-        <v>316</v>
+        <v>354</v>
       </c>
       <c r="C3" t="s">
         <v>78</v>
@@ -2203,7 +2317,7 @@
         <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>317</v>
+        <v>355</v>
       </c>
       <c r="C4" t="s">
         <v>78</v>
@@ -2307,7 +2421,7 @@
         <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>318</v>
+        <v>356</v>
       </c>
       <c r="C5" t="s">
         <v>78</v>
@@ -2537,7 +2651,7 @@
         <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="C2" t="s">
         <v>78</v>
@@ -2638,7 +2752,7 @@
         <v>78</v>
       </c>
       <c r="B3" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="C3" t="s">
         <v>78</v>
@@ -2739,7 +2853,7 @@
         <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
       <c r="C4" t="s">
         <v>78</v>
@@ -2840,7 +2954,7 @@
         <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>322</v>
+        <v>360</v>
       </c>
       <c r="C5" t="s">
         <v>78</v>
@@ -3065,7 +3179,7 @@
         <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>303</v>
+        <v>341</v>
       </c>
       <c r="C2" t="s">
         <v>78</v>
@@ -3166,7 +3280,7 @@
         <v>78</v>
       </c>
       <c r="B3" t="s">
-        <v>304</v>
+        <v>342</v>
       </c>
       <c r="C3" t="s">
         <v>78</v>
@@ -3267,7 +3381,7 @@
         <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>305</v>
+        <v>343</v>
       </c>
       <c r="C4" t="s">
         <v>78</v>
@@ -3368,7 +3482,7 @@
         <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>306</v>
+        <v>344</v>
       </c>
       <c r="C5" t="s">
         <v>78</v>
@@ -4115,7 +4229,7 @@
         <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>307</v>
+        <v>345</v>
       </c>
       <c r="C2" t="s">
         <v>78</v>
@@ -4219,7 +4333,7 @@
         <v>78</v>
       </c>
       <c r="B3" t="s">
-        <v>308</v>
+        <v>346</v>
       </c>
       <c r="C3" t="s">
         <v>78</v>
@@ -4323,7 +4437,7 @@
         <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>309</v>
+        <v>347</v>
       </c>
       <c r="C4" t="s">
         <v>78</v>
@@ -4427,7 +4541,7 @@
         <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="C5" t="s">
         <v>78</v>
@@ -4659,7 +4773,7 @@
         <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>285</v>
+        <v>323</v>
       </c>
       <c r="C2" t="s">
         <v>78</v>
@@ -4766,7 +4880,7 @@
         <v>78</v>
       </c>
       <c r="B3" t="s">
-        <v>286</v>
+        <v>324</v>
       </c>
       <c r="C3" t="s">
         <v>78</v>
@@ -4873,7 +4987,7 @@
         <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>287</v>
+        <v>325</v>
       </c>
       <c r="C4" t="s">
         <v>78</v>
@@ -4980,7 +5094,7 @@
         <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="C5" t="s">
         <v>78</v>
@@ -5087,7 +5201,7 @@
         <v>78</v>
       </c>
       <c r="B6" t="s">
-        <v>289</v>
+        <v>327</v>
       </c>
       <c r="C6" t="s">
         <v>78</v>
@@ -5194,7 +5308,7 @@
         <v>78</v>
       </c>
       <c r="B7" t="s">
-        <v>290</v>
+        <v>328</v>
       </c>
       <c r="C7" t="s">
         <v>78</v>
@@ -5428,7 +5542,7 @@
         <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>291</v>
+        <v>329</v>
       </c>
       <c r="C2" t="s">
         <v>78</v>
@@ -5535,7 +5649,7 @@
         <v>78</v>
       </c>
       <c r="B3" t="s">
-        <v>292</v>
+        <v>330</v>
       </c>
       <c r="C3" t="s">
         <v>78</v>
@@ -5642,7 +5756,7 @@
         <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>293</v>
+        <v>331</v>
       </c>
       <c r="C4" t="s">
         <v>78</v>
@@ -5749,7 +5863,7 @@
         <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>294</v>
+        <v>332</v>
       </c>
       <c r="C5" t="s">
         <v>78</v>
@@ -5856,7 +5970,7 @@
         <v>78</v>
       </c>
       <c r="B6" t="s">
-        <v>295</v>
+        <v>333</v>
       </c>
       <c r="C6" t="s">
         <v>78</v>
@@ -5963,7 +6077,7 @@
         <v>78</v>
       </c>
       <c r="B7" t="s">
-        <v>296</v>
+        <v>334</v>
       </c>
       <c r="C7" t="s">
         <v>78</v>
@@ -6196,7 +6310,7 @@
         <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>297</v>
+        <v>335</v>
       </c>
       <c r="C2" t="s">
         <v>78</v>
@@ -6300,7 +6414,7 @@
         <v>78</v>
       </c>
       <c r="B3" t="s">
-        <v>298</v>
+        <v>336</v>
       </c>
       <c r="C3" t="s">
         <v>78</v>
@@ -6404,7 +6518,7 @@
         <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>299</v>
+        <v>337</v>
       </c>
       <c r="C4" t="s">
         <v>78</v>
@@ -6508,7 +6622,7 @@
         <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>300</v>
+        <v>338</v>
       </c>
       <c r="C5" t="s">
         <v>78</v>
@@ -6612,7 +6726,7 @@
         <v>78</v>
       </c>
       <c r="B6" t="s">
-        <v>301</v>
+        <v>339</v>
       </c>
       <c r="C6" t="s">
         <v>78</v>
@@ -6716,7 +6830,7 @@
         <v>78</v>
       </c>
       <c r="B7" t="s">
-        <v>302</v>
+        <v>340</v>
       </c>
       <c r="C7" t="s">
         <v>78</v>

--- a/KatalonData/Bootstrap/VT-Data-Prod.xlsx
+++ b/KatalonData/Bootstrap/VT-Data-Prod.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2560" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3052" uniqueCount="484">
   <si>
     <t>AppIDDemo</t>
   </si>
@@ -1116,6 +1116,375 @@
   </si>
   <si>
     <t>Wed Apr 22 22:32:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:18:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:19:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:21:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:22:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:23:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:25:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:26:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:27:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:28:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:30:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:31:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:32:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:10:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:11:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:12:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:13:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:14:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:15:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:16:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:17:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:18:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:19:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:19:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:20:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:21:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:22:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:23:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:24:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:24:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:25:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:26:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:27:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:28:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:28:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:29:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:31:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:31:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:32:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:33:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:34:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:34:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 01:35:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:18:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:20:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:21:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:22:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:24:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:25:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:36:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:37:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:39:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:40:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:41:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:43:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:48:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:49:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:51:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:52:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:54:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 19:55:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 20:03:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 20:07:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 20:09:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 20:10:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 20:34:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 20:35:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 20:36:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 20:38:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:32:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:33:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:34:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:36:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:37:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:38:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:40:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:41:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:42:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:43:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:44:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:45:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:40:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:41:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:42:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:43:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:44:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:45:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:46:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:47:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:47:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:48:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:49:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:54:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:55:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:56:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:57:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:58:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:59:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 01:59:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 02:00:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 02:04:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 02:05:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 02:06:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 02:06:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 02:07:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 02:08:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 02:09:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 02:09:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 20:53:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 20:55:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 20:56:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 20:57:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 20:59:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 21:00:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 21:34:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 21:36:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 21:37:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 21:39:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 21:40:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 21:41:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 21:54:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 21:55:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 21:56:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 21:57:00 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1577,7 +1946,7 @@
         <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>349</v>
+        <v>456</v>
       </c>
       <c r="C2" t="s">
         <v>78</v>
@@ -1678,7 +2047,7 @@
         <v>78</v>
       </c>
       <c r="B3" t="s">
-        <v>350</v>
+        <v>457</v>
       </c>
       <c r="C3" t="s">
         <v>78</v>
@@ -1779,7 +2148,7 @@
         <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>351</v>
+        <v>458</v>
       </c>
       <c r="C4" t="s">
         <v>78</v>
@@ -1880,7 +2249,7 @@
         <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>352</v>
+        <v>459</v>
       </c>
       <c r="C5" t="s">
         <v>78</v>
@@ -2115,7 +2484,7 @@
         <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>277</v>
+        <v>460</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
@@ -2219,7 +2588,7 @@
         <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>278</v>
+        <v>461</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
@@ -2323,7 +2692,7 @@
         <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>279</v>
+        <v>462</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
@@ -2427,7 +2796,7 @@
         <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>280</v>
+        <v>463</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
@@ -2651,7 +3020,7 @@
         <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>357</v>
+        <v>464</v>
       </c>
       <c r="C2" t="s">
         <v>78</v>
@@ -2752,7 +3121,7 @@
         <v>78</v>
       </c>
       <c r="B3" t="s">
-        <v>358</v>
+        <v>465</v>
       </c>
       <c r="C3" t="s">
         <v>78</v>
@@ -2853,7 +3222,7 @@
         <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>359</v>
+        <v>466</v>
       </c>
       <c r="C4" t="s">
         <v>78</v>
@@ -2954,7 +3323,7 @@
         <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>360</v>
+        <v>467</v>
       </c>
       <c r="C5" t="s">
         <v>78</v>
@@ -3179,7 +3548,7 @@
         <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>341</v>
+        <v>447</v>
       </c>
       <c r="C2" t="s">
         <v>78</v>
@@ -3280,7 +3649,7 @@
         <v>78</v>
       </c>
       <c r="B3" t="s">
-        <v>342</v>
+        <v>448</v>
       </c>
       <c r="C3" t="s">
         <v>78</v>
@@ -3381,7 +3750,7 @@
         <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>343</v>
+        <v>449</v>
       </c>
       <c r="C4" t="s">
         <v>78</v>
@@ -3482,7 +3851,7 @@
         <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>344</v>
+        <v>450</v>
       </c>
       <c r="C5" t="s">
         <v>78</v>
@@ -3706,7 +4075,7 @@
         <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>265</v>
+        <v>480</v>
       </c>
       <c r="C2" t="s">
         <v>78</v>
@@ -3805,7 +4174,7 @@
         <v>78</v>
       </c>
       <c r="B3" t="s">
-        <v>266</v>
+        <v>481</v>
       </c>
       <c r="C3" t="s">
         <v>78</v>
@@ -3904,7 +4273,7 @@
         <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>267</v>
+        <v>482</v>
       </c>
       <c r="C4" t="s">
         <v>78</v>
@@ -4003,7 +4372,7 @@
         <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>268</v>
+        <v>483</v>
       </c>
       <c r="C5" t="s">
         <v>78</v>
@@ -4229,10 +4598,10 @@
         <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>345</v>
+        <v>452</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
@@ -4333,10 +4702,10 @@
         <v>78</v>
       </c>
       <c r="B3" t="s">
-        <v>346</v>
+        <v>453</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
@@ -4437,10 +4806,10 @@
         <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>347</v>
+        <v>454</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
@@ -4541,10 +4910,10 @@
         <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>348</v>
+        <v>455</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
@@ -4779,7 +5148,7 @@
         <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>243</v>
+        <v>474</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
@@ -4886,7 +5255,7 @@
         <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>244</v>
+        <v>475</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
@@ -4990,10 +5359,10 @@
         <v>325</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>245</v>
+        <v>476</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
@@ -5097,10 +5466,10 @@
         <v>326</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>246</v>
+        <v>477</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
@@ -5207,7 +5576,7 @@
         <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>247</v>
+        <v>478</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
@@ -5314,7 +5683,7 @@
         <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>248</v>
+        <v>479</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
@@ -5548,7 +5917,7 @@
         <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>249</v>
+        <v>435</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
@@ -5655,7 +6024,7 @@
         <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>250</v>
+        <v>436</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
@@ -5762,7 +6131,7 @@
         <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>251</v>
+        <v>437</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
@@ -5869,7 +6238,7 @@
         <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>252</v>
+        <v>438</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
@@ -5976,7 +6345,7 @@
         <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>253</v>
+        <v>439</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
@@ -6083,7 +6452,7 @@
         <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>254</v>
+        <v>440</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
@@ -6310,7 +6679,7 @@
         <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>335</v>
+        <v>441</v>
       </c>
       <c r="C2" t="s">
         <v>78</v>
@@ -6414,7 +6783,7 @@
         <v>78</v>
       </c>
       <c r="B3" t="s">
-        <v>336</v>
+        <v>442</v>
       </c>
       <c r="C3" t="s">
         <v>78</v>
@@ -6518,7 +6887,7 @@
         <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>337</v>
+        <v>443</v>
       </c>
       <c r="C4" t="s">
         <v>78</v>
@@ -6622,7 +6991,7 @@
         <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>338</v>
+        <v>444</v>
       </c>
       <c r="C5" t="s">
         <v>78</v>
@@ -6726,7 +7095,7 @@
         <v>78</v>
       </c>
       <c r="B6" t="s">
-        <v>339</v>
+        <v>445</v>
       </c>
       <c r="C6" t="s">
         <v>78</v>
@@ -6830,7 +7199,7 @@
         <v>78</v>
       </c>
       <c r="B7" t="s">
-        <v>340</v>
+        <v>446</v>
       </c>
       <c r="C7" t="s">
         <v>78</v>

--- a/KatalonData/Bootstrap/VT-Data-Prod.xlsx
+++ b/KatalonData/Bootstrap/VT-Data-Prod.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3052" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3068" uniqueCount="492">
   <si>
     <t>AppIDDemo</t>
   </si>
@@ -1485,6 +1485,30 @@
   </si>
   <si>
     <t>Fri Jun 19 21:57:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:34:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:35:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:37:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:38:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:39:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:39:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:40:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:41:41 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -1822,7 +1846,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AK5"/>
+  <dimension ref="A1:AJ5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="34.88671875" collapsed="true"/>
@@ -1942,13 +1966,13 @@
       </c>
     </row>
     <row ht="57.6" r="2" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>456</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E2" s="1"/>
@@ -2043,13 +2067,13 @@
       </c>
     </row>
     <row ht="57.6" r="3" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>457</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E3" s="1"/>
@@ -2144,13 +2168,13 @@
       </c>
     </row>
     <row ht="57.6" r="4" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s" s="0">
         <v>458</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E4" s="1"/>
@@ -2245,13 +2269,13 @@
       </c>
     </row>
     <row ht="57.6" r="5" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>459</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E5" s="1"/>
@@ -2355,7 +2379,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{785E5B8F-F388-454B-9312-37D5E8A239CA}">
-  <dimension ref="A1:AK5"/>
+  <dimension ref="A1:AJ5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="42.88671875" collapsed="true"/>
@@ -2474,16 +2498,16 @@
       </c>
     </row>
     <row ht="43.2" r="2" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>353</v>
       </c>
-      <c r="C2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D2" t="s" s="0">
         <v>460</v>
       </c>
       <c r="E2" s="1"/>
@@ -2578,16 +2602,16 @@
       </c>
     </row>
     <row ht="43.2" r="3" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>354</v>
       </c>
-      <c r="C3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D3" t="s" s="0">
         <v>461</v>
       </c>
       <c r="E3" s="1"/>
@@ -2682,16 +2706,16 @@
       </c>
     </row>
     <row ht="43.2" r="4" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s" s="0">
         <v>355</v>
       </c>
-      <c r="C4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C4" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D4" t="s" s="0">
         <v>462</v>
       </c>
       <c r="E4" s="1"/>
@@ -2786,16 +2810,16 @@
       </c>
     </row>
     <row ht="43.2" r="5" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>356</v>
       </c>
-      <c r="C5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C5" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D5" t="s" s="0">
         <v>463</v>
       </c>
       <c r="E5" s="1"/>
@@ -2896,7 +2920,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14398818-C378-4625-9C7B-8B7A60808E50}">
-  <dimension ref="A1:AK5"/>
+  <dimension ref="A1:AJ5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="46.88671875" collapsed="true"/>
@@ -3016,13 +3040,13 @@
       </c>
     </row>
     <row ht="57.6" r="2" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>464</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E2" s="1"/>
@@ -3117,13 +3141,13 @@
       </c>
     </row>
     <row ht="57.6" r="3" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>465</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E3" s="1"/>
@@ -3218,13 +3242,13 @@
       </c>
     </row>
     <row ht="57.6" r="4" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s" s="0">
         <v>466</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E4" s="1"/>
@@ -3319,13 +3343,13 @@
       </c>
     </row>
     <row ht="57.6" r="5" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>467</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E5" s="1"/>
@@ -3426,7 +3450,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F80835E-80C2-4B5E-A27D-BEE82C4EA194}">
-  <dimension ref="A1:AK5"/>
+  <dimension ref="A1:AJ5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" customWidth="true" width="44.5546875" collapsed="true"/>
@@ -3544,13 +3568,13 @@
       </c>
     </row>
     <row ht="57.6" r="2" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>447</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E2" s="1"/>
@@ -3645,13 +3669,13 @@
       </c>
     </row>
     <row ht="57.6" r="3" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>448</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E3" s="1"/>
@@ -3746,13 +3770,13 @@
       </c>
     </row>
     <row ht="57.6" r="4" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s" s="0">
         <v>449</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E4" s="1"/>
@@ -3847,13 +3871,13 @@
       </c>
     </row>
     <row ht="57.6" r="5" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>450</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E5" s="1"/>
@@ -3954,7 +3978,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DCA27D4-E8CC-4524-89F3-92615FB855D9}">
-  <dimension ref="A1:AK5"/>
+  <dimension ref="A1:AJ5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="4" customWidth="true" width="27.0" collapsed="true"/>
@@ -4071,13 +4095,13 @@
       </c>
     </row>
     <row ht="43.2" r="2" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>480</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E2" s="1"/>
@@ -4170,13 +4194,13 @@
       </c>
     </row>
     <row ht="43.2" r="3" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>481</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E3" s="1"/>
@@ -4269,13 +4293,13 @@
       </c>
     </row>
     <row ht="43.2" r="4" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s" s="0">
         <v>482</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E4" s="1"/>
@@ -4368,13 +4392,13 @@
       </c>
     </row>
     <row ht="43.2" r="5" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>483</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E5" s="1"/>
@@ -4473,7 +4497,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15419439-C550-4DF2-A35F-21D8EAD8595F}">
-  <dimension ref="A1:AL5"/>
+  <dimension ref="A1:AK5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="4" customWidth="true" width="35.33203125" collapsed="true"/>
@@ -4594,13 +4618,13 @@
       </c>
     </row>
     <row ht="57.6" r="2" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>452</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>81</v>
       </c>
       <c r="E2" s="1"/>
@@ -4698,13 +4722,13 @@
       </c>
     </row>
     <row ht="57.6" r="3" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>453</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>81</v>
       </c>
       <c r="E3" s="1"/>
@@ -4802,13 +4826,13 @@
       </c>
     </row>
     <row ht="57.6" r="4" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s" s="0">
         <v>454</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="0">
         <v>81</v>
       </c>
       <c r="E4" s="1"/>
@@ -4906,13 +4930,13 @@
       </c>
     </row>
     <row ht="57.6" r="5" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>455</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="0">
         <v>81</v>
       </c>
       <c r="E5" s="1"/>
@@ -5016,7 +5040,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C1DA7C8-561B-4DB6-AEC9-913575D04D9C}">
-  <dimension ref="A1:AL7"/>
+  <dimension ref="A1:AK7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="4" customWidth="true" width="28.33203125" collapsed="true"/>
@@ -5138,16 +5162,16 @@
       </c>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>484</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D2" t="s" s="0">
         <v>474</v>
       </c>
       <c r="E2" s="2"/>
@@ -5245,16 +5269,16 @@
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" t="s">
-        <v>324</v>
-      </c>
-      <c r="C3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>485</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D3" t="s" s="0">
         <v>475</v>
       </c>
       <c r="E3" s="2"/>
@@ -5352,16 +5376,16 @@
       </c>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s" s="0">
         <v>325</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" t="s" s="0">
         <v>476</v>
       </c>
       <c r="E4" s="2"/>
@@ -5459,16 +5483,16 @@
       </c>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>326</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" t="s" s="0">
         <v>477</v>
       </c>
       <c r="E5" s="2"/>
@@ -5566,16 +5590,16 @@
       </c>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="A6" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B6" t="s" s="0">
         <v>327</v>
       </c>
-      <c r="C6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C6" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D6" t="s" s="0">
         <v>478</v>
       </c>
       <c r="E6" s="2"/>
@@ -5673,16 +5697,16 @@
       </c>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="A7" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B7" t="s" s="0">
         <v>328</v>
       </c>
-      <c r="C7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C7" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D7" t="s" s="0">
         <v>479</v>
       </c>
       <c r="E7" s="2"/>
@@ -5786,7 +5810,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0F298BB-BA96-478C-B434-E08D216C7BCB}">
-  <dimension ref="A1:AL7"/>
+  <dimension ref="A1:AK7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="4" customWidth="true" width="43.44140625" collapsed="true"/>
@@ -5907,16 +5931,16 @@
       </c>
     </row>
     <row ht="43.2" r="2" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>486</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D2" t="s" s="0">
         <v>435</v>
       </c>
       <c r="E2" s="1"/>
@@ -6014,16 +6038,16 @@
       </c>
     </row>
     <row ht="43.2" r="3" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" t="s">
-        <v>330</v>
-      </c>
-      <c r="C3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>487</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D3" t="s" s="0">
         <v>436</v>
       </c>
       <c r="E3" s="1"/>
@@ -6121,16 +6145,16 @@
       </c>
     </row>
     <row ht="57.6" r="4" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" t="s">
-        <v>331</v>
-      </c>
-      <c r="C4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="A4" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>488</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D4" t="s" s="0">
         <v>437</v>
       </c>
       <c r="E4" s="1"/>
@@ -6228,16 +6252,16 @@
       </c>
     </row>
     <row ht="57.6" r="5" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" t="s">
-        <v>332</v>
-      </c>
-      <c r="C5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="A5" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>489</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D5" t="s" s="0">
         <v>438</v>
       </c>
       <c r="E5" s="1"/>
@@ -6335,16 +6359,16 @@
       </c>
     </row>
     <row ht="57.6" r="6" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" t="s">
-        <v>333</v>
-      </c>
-      <c r="C6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="A6" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>490</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D6" t="s" s="0">
         <v>439</v>
       </c>
       <c r="E6" s="1"/>
@@ -6442,16 +6466,16 @@
       </c>
     </row>
     <row ht="57.6" r="7" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" t="s">
-        <v>334</v>
-      </c>
-      <c r="C7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="A7" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>491</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D7" t="s" s="0">
         <v>440</v>
       </c>
       <c r="E7" s="1"/>
@@ -6555,7 +6579,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BE28CED-02AF-4422-B87F-90E9A0FAAB78}">
-  <dimension ref="A1:AL7"/>
+  <dimension ref="A1:AK7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="4" customWidth="true" width="35.88671875" collapsed="true"/>
@@ -6675,13 +6699,13 @@
       </c>
     </row>
     <row ht="43.2" r="2" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>441</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E2" s="1"/>
@@ -6779,13 +6803,13 @@
       </c>
     </row>
     <row ht="43.2" r="3" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>442</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E3" s="1"/>
@@ -6883,13 +6907,13 @@
       </c>
     </row>
     <row ht="57.6" r="4" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s" s="0">
         <v>443</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E4" s="1"/>
@@ -6987,13 +7011,13 @@
       </c>
     </row>
     <row ht="57.6" r="5" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>444</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E5" s="1"/>
@@ -7091,13 +7115,13 @@
       </c>
     </row>
     <row ht="57.6" r="6" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="A6" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B6" t="s" s="0">
         <v>445</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E6" s="1"/>
@@ -7195,13 +7219,13 @@
       </c>
     </row>
     <row ht="57.6" r="7" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="A7" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B7" t="s" s="0">
         <v>446</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E7" s="1"/>

--- a/KatalonData/Bootstrap/VT-Data-Prod.xlsx
+++ b/KatalonData/Bootstrap/VT-Data-Prod.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3052" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3448" uniqueCount="682">
   <si>
     <t>AppIDDemo</t>
   </si>
@@ -1485,6 +1485,600 @@
   </si>
   <si>
     <t>Fri Jun 19 21:57:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:56:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:57:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:59:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:00:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:01:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:03:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:04:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:05:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:07:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:08:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:09:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:10:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:39:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:40:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:41:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:42:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:43:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:44:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:44:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:46:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:46:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:47:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:48:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:49:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:50:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:51:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:51:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:52:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:53:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:53:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:54:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:55:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:56:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:57:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:57:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:58:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 23:59:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 01 00:00:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 01 00:01:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 01 00:02:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 01 00:02:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 01 00:03:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:23:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:25:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:26:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:27:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:28:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:30:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:31:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:32:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:33:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:34:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:35:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:36:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:04:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:05:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:06:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:07:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:08:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:08:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:09:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:10:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:11:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:11:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:12:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:13:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:14:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:14:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:15:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:16:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:16:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:17:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:18:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:19:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:20:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:20:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:21:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:22:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:22:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:23:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:24:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:24:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:25:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 21:26:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:23:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:24:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:26:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:27:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:28:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:30:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:31:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:33:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:34:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:36:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:37:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:39:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:15:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:16:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:17:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:18:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:19:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:20:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:21:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:23:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:24:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:24:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:26:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:27:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:28:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:28:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:29:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:30:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:32:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:32:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:33:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:34:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:36:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:36:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:37:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:38:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:40:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 18:41:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:52:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:54:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:56:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:57:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:59:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:00:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:02:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:03:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:04:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:06:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:07:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:09:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:45:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:46:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:47:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:48:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:49:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:50:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:51:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:52:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:53:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:54:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:56:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:57:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:58:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:58:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 17:59:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 18:01:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 18:01:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 18:02:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 18:03:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 18:05:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 18:06:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 18:07:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 18:08:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 18:09:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 18:09:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 18:11:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:50:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:51:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:53:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:54:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:56:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:57:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:59:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:00:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:01:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:03:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:04:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:05:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:40:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:41:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:42:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:43:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:44:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:45:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:46:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:47:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:48:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:48:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:49:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:50:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:51:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:52:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:53:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:54:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:55:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:56:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:57:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:58:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 07:59:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 08:00:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 08:01:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 08:01:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 08:02:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 08:03:32 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1822,7 +2416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AK5"/>
+  <dimension ref="A1:AJ5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="34.88671875" collapsed="true"/>
@@ -1942,13 +2536,13 @@
       </c>
     </row>
     <row ht="57.6" r="2" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" t="s">
-        <v>456</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>670</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E2" s="1"/>
@@ -2043,13 +2637,13 @@
       </c>
     </row>
     <row ht="57.6" r="3" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" t="s">
-        <v>457</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>671</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E3" s="1"/>
@@ -2144,13 +2738,13 @@
       </c>
     </row>
     <row ht="57.6" r="4" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" t="s">
-        <v>458</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="A4" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>672</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E4" s="1"/>
@@ -2245,13 +2839,13 @@
       </c>
     </row>
     <row ht="57.6" r="5" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" t="s">
-        <v>459</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="A5" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>673</v>
+      </c>
+      <c r="C5" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E5" s="1"/>
@@ -2355,7 +2949,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{785E5B8F-F388-454B-9312-37D5E8A239CA}">
-  <dimension ref="A1:AK5"/>
+  <dimension ref="A1:AJ5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="42.88671875" collapsed="true"/>
@@ -2474,17 +3068,17 @@
       </c>
     </row>
     <row ht="43.2" r="2" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" t="s">
-        <v>353</v>
-      </c>
-      <c r="C2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D2" t="s">
-        <v>460</v>
+      <c r="A2" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>674</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>560</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
@@ -2578,17 +3172,17 @@
       </c>
     </row>
     <row ht="43.2" r="3" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" t="s">
-        <v>461</v>
+      <c r="A3" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>675</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>561</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
@@ -2682,17 +3276,17 @@
       </c>
     </row>
     <row ht="43.2" r="4" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" t="s">
-        <v>355</v>
-      </c>
-      <c r="C4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" t="s">
-        <v>462</v>
+      <c r="A4" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>676</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>562</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
@@ -2786,17 +3380,17 @@
       </c>
     </row>
     <row ht="43.2" r="5" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" t="s">
-        <v>356</v>
-      </c>
-      <c r="C5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" t="s">
-        <v>463</v>
+      <c r="A5" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>677</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>563</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
@@ -2896,7 +3490,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14398818-C378-4625-9C7B-8B7A60808E50}">
-  <dimension ref="A1:AK5"/>
+  <dimension ref="A1:AJ5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" customWidth="true" width="46.88671875" collapsed="true"/>
@@ -3016,13 +3610,13 @@
       </c>
     </row>
     <row ht="57.6" r="2" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" t="s">
-        <v>464</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>678</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E2" s="1"/>
@@ -3117,13 +3711,13 @@
       </c>
     </row>
     <row ht="57.6" r="3" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" t="s">
-        <v>465</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>679</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E3" s="1"/>
@@ -3218,13 +3812,13 @@
       </c>
     </row>
     <row ht="57.6" r="4" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" t="s">
-        <v>466</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="A4" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>680</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E4" s="1"/>
@@ -3319,13 +3913,13 @@
       </c>
     </row>
     <row ht="57.6" r="5" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" t="s">
-        <v>467</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="A5" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>681</v>
+      </c>
+      <c r="C5" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E5" s="1"/>
@@ -3426,7 +4020,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F80835E-80C2-4B5E-A27D-BEE82C4EA194}">
-  <dimension ref="A1:AK5"/>
+  <dimension ref="A1:AJ5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" customWidth="true" width="44.5546875" collapsed="true"/>
@@ -3544,13 +4138,13 @@
       </c>
     </row>
     <row ht="57.6" r="2" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" t="s">
-        <v>447</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>662</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E2" s="1"/>
@@ -3645,13 +4239,13 @@
       </c>
     </row>
     <row ht="57.6" r="3" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" t="s">
-        <v>448</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>663</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E3" s="1"/>
@@ -3746,13 +4340,13 @@
       </c>
     </row>
     <row ht="57.6" r="4" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" t="s">
-        <v>449</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="A4" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>664</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E4" s="1"/>
@@ -3847,13 +4441,13 @@
       </c>
     </row>
     <row ht="57.6" r="5" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" t="s">
-        <v>450</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="A5" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>665</v>
+      </c>
+      <c r="C5" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E5" s="1"/>
@@ -3954,7 +4548,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DCA27D4-E8CC-4524-89F3-92615FB855D9}">
-  <dimension ref="A1:AK5"/>
+  <dimension ref="A1:AJ5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="4" customWidth="true" width="27.0" collapsed="true"/>
@@ -4071,13 +4665,13 @@
       </c>
     </row>
     <row ht="43.2" r="2" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" t="s">
-        <v>480</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>548</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E2" s="1"/>
@@ -4170,13 +4764,13 @@
       </c>
     </row>
     <row ht="43.2" r="3" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" t="s">
-        <v>481</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>549</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E3" s="1"/>
@@ -4269,13 +4863,13 @@
       </c>
     </row>
     <row ht="43.2" r="4" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" t="s">
-        <v>482</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="A4" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>550</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E4" s="1"/>
@@ -4368,13 +4962,13 @@
       </c>
     </row>
     <row ht="43.2" r="5" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" t="s">
-        <v>483</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="A5" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>551</v>
+      </c>
+      <c r="C5" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E5" s="1"/>
@@ -4473,7 +5067,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15419439-C550-4DF2-A35F-21D8EAD8595F}">
-  <dimension ref="A1:AL5"/>
+  <dimension ref="A1:AK5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="4" customWidth="true" width="35.33203125" collapsed="true"/>
@@ -4594,14 +5188,14 @@
       </c>
     </row>
     <row ht="57.6" r="2" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C2" t="s">
-        <v>81</v>
+      <c r="A2" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>666</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>78</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
@@ -4698,14 +5292,14 @@
       </c>
     </row>
     <row ht="57.6" r="3" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" t="s">
-        <v>453</v>
-      </c>
-      <c r="C3" t="s">
-        <v>81</v>
+      <c r="A3" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>667</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>78</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
@@ -4802,14 +5396,14 @@
       </c>
     </row>
     <row ht="57.6" r="4" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" t="s">
-        <v>454</v>
-      </c>
-      <c r="C4" t="s">
-        <v>81</v>
+      <c r="A4" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>668</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>78</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
@@ -4906,14 +5500,14 @@
       </c>
     </row>
     <row ht="57.6" r="5" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" t="s">
-        <v>455</v>
-      </c>
-      <c r="C5" t="s">
-        <v>81</v>
+      <c r="A5" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>669</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>78</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
@@ -5016,7 +5610,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C1DA7C8-561B-4DB6-AEC9-913575D04D9C}">
-  <dimension ref="A1:AL7"/>
+  <dimension ref="A1:AK7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="4" customWidth="true" width="28.33203125" collapsed="true"/>
@@ -5138,17 +5732,17 @@
       </c>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D2" t="s">
-        <v>474</v>
+      <c r="A2" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>644</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>526</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
@@ -5245,17 +5839,17 @@
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" t="s">
-        <v>324</v>
-      </c>
-      <c r="C3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" t="s">
-        <v>475</v>
+      <c r="A3" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>645</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>527</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
@@ -5352,17 +5946,17 @@
       </c>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" t="s">
-        <v>325</v>
-      </c>
-      <c r="C4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D4" t="s">
-        <v>476</v>
+      <c r="A4" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>646</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>528</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
@@ -5459,17 +6053,17 @@
       </c>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" t="s">
-        <v>326</v>
-      </c>
-      <c r="C5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" t="s">
-        <v>477</v>
+      <c r="A5" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>647</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>529</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
@@ -5566,17 +6160,17 @@
       </c>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" t="s">
-        <v>327</v>
-      </c>
-      <c r="C6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" t="s">
-        <v>478</v>
+      <c r="A6" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>648</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>530</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
@@ -5673,17 +6267,17 @@
       </c>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" t="s">
-        <v>328</v>
-      </c>
-      <c r="C7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" t="s">
-        <v>479</v>
+      <c r="A7" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>649</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>531</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
@@ -5786,7 +6380,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0F298BB-BA96-478C-B434-E08D216C7BCB}">
-  <dimension ref="A1:AL7"/>
+  <dimension ref="A1:AK7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="4" customWidth="true" width="43.44140625" collapsed="true"/>
@@ -5907,17 +6501,17 @@
       </c>
     </row>
     <row ht="43.2" r="2" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D2" t="s">
-        <v>435</v>
+      <c r="A2" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>650</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>532</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
@@ -6014,17 +6608,17 @@
       </c>
     </row>
     <row ht="43.2" r="3" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" t="s">
-        <v>330</v>
-      </c>
-      <c r="C3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" t="s">
-        <v>436</v>
+      <c r="A3" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>651</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>533</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
@@ -6121,17 +6715,17 @@
       </c>
     </row>
     <row ht="57.6" r="4" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" t="s">
-        <v>331</v>
-      </c>
-      <c r="C4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" t="s">
-        <v>437</v>
+      <c r="A4" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>652</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>534</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
@@ -6228,17 +6822,17 @@
       </c>
     </row>
     <row ht="57.6" r="5" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" t="s">
-        <v>332</v>
-      </c>
-      <c r="C5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" t="s">
-        <v>438</v>
+      <c r="A5" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>653</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>535</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
@@ -6335,17 +6929,17 @@
       </c>
     </row>
     <row ht="57.6" r="6" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" t="s">
-        <v>333</v>
-      </c>
-      <c r="C6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" t="s">
-        <v>439</v>
+      <c r="A6" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>654</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>536</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
@@ -6442,17 +7036,17 @@
       </c>
     </row>
     <row ht="57.6" r="7" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" t="s">
-        <v>334</v>
-      </c>
-      <c r="C7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" t="s">
-        <v>440</v>
+      <c r="A7" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>655</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>537</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
@@ -6555,7 +7149,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BE28CED-02AF-4422-B87F-90E9A0FAAB78}">
-  <dimension ref="A1:AL7"/>
+  <dimension ref="A1:AK7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="4" customWidth="true" width="35.88671875" collapsed="true"/>
@@ -6675,13 +7269,13 @@
       </c>
     </row>
     <row ht="43.2" r="2" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" t="s">
-        <v>441</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>656</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E2" s="1"/>
@@ -6779,13 +7373,13 @@
       </c>
     </row>
     <row ht="43.2" r="3" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" t="s">
-        <v>442</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>657</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E3" s="1"/>
@@ -6883,13 +7477,13 @@
       </c>
     </row>
     <row ht="57.6" r="4" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" t="s">
-        <v>443</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="A4" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>658</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E4" s="1"/>
@@ -6987,13 +7581,13 @@
       </c>
     </row>
     <row ht="57.6" r="5" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" t="s">
-        <v>444</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="A5" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>659</v>
+      </c>
+      <c r="C5" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E5" s="1"/>
@@ -7091,13 +7685,13 @@
       </c>
     </row>
     <row ht="57.6" r="6" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" t="s">
-        <v>445</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="A6" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>660</v>
+      </c>
+      <c r="C6" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E6" s="1"/>
@@ -7195,13 +7789,13 @@
       </c>
     </row>
     <row ht="57.6" r="7" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" t="s">
-        <v>446</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="A7" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>661</v>
+      </c>
+      <c r="C7" t="s" s="0">
         <v>78</v>
       </c>
       <c r="E7" s="1"/>
